--- a/Collections/EURO/Lithuania/#EURO#Lithuania#Commemorative#[2015-present]#UNC.xlsx
+++ b/Collections/EURO/Lithuania/#EURO#Lithuania#Commemorative#[2015-present]#UNC.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lord_Alexator\Documents\CoinCollection\Collections\EURO\Lithuania\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E057ABB3-78F9-431C-BBA5-F246D40B8922}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C14347AD-A544-4957-A12F-B38981F2EF56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,6 +32,9 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -80,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="56">
   <si>
     <t>Year</t>
   </si>
@@ -242,6 +245,12 @@
   </si>
   <si>
     <t>Subtype_4#Special_distinctions_1</t>
+  </si>
+  <si>
+    <t>Lithuania Minor</t>
+  </si>
+  <si>
+    <t>Energy Independence of Lithuania</t>
   </si>
 </sst>
 </file>
@@ -251,7 +260,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0\ [$€-1];[Red]\-#,##0\ [$€-1]"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -307,6 +316,10 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="204"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="7">
@@ -534,7 +547,15 @@
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
     <cellStyle name="Обычный 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
   </cellStyles>
-  <dxfs count="14">
+  <dxfs count="15">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -653,9 +674,9 @@
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="№" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Link" dataDxfId="1" dataCellStyle="Гиперссылка"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description (single table, table set, mintage, prices):" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="№" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Link" dataDxfId="2" dataCellStyle="Гиперссылка"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description (single table, table set, mintage, prices):" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="1" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -1484,7 +1505,61 @@
         <v>1</v>
       </c>
       <c r="I21" s="7" t="str">
-        <f t="shared" ref="I21" si="7">IF(OR(AND(H21&gt;1,H21&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" ref="I21:I22" si="7">IF(OR(AND(H21&gt;1,H21&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="22">
+        <v>2026</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C22" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="D22" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="F22" s="6"/>
+      <c r="G22" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="H22" s="18">
+        <v>1</v>
+      </c>
+      <c r="I22" s="7" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="22">
+        <v>2026</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C23" s="23"/>
+      <c r="D23" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="F23" s="6"/>
+      <c r="G23" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="H23" s="18">
+        <v>0</v>
+      </c>
+      <c r="I23" s="7" t="str">
+        <f t="shared" ref="I23" si="8">IF(OR(AND(H23&gt;1,H23&lt;&gt;"-")),"Can exchange","")</f>
         <v/>
       </c>
     </row>
@@ -1502,12 +1577,30 @@
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="C1:F1"/>
   </mergeCells>
+  <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="H3:H10">
+    <cfRule type="containsText" dxfId="14" priority="31" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H3))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H3:H10">
+    <cfRule type="colorScale" priority="32">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H11">
     <cfRule type="containsText" dxfId="13" priority="29" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H3))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H3:H10">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H11))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H11">
     <cfRule type="colorScale" priority="30">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -1519,12 +1612,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H11">
+  <conditionalFormatting sqref="H12">
     <cfRule type="containsText" dxfId="12" priority="27" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H11))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H11">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H12))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H12">
     <cfRule type="colorScale" priority="28">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -1536,13 +1629,13 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H12">
-    <cfRule type="containsText" dxfId="11" priority="25" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H12))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H12">
-    <cfRule type="colorScale" priority="26">
+  <conditionalFormatting sqref="H13">
+    <cfRule type="containsText" dxfId="11" priority="21" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H13))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H13">
+    <cfRule type="colorScale" priority="22">
       <colorScale>
         <cfvo type="formula" val="0"/>
         <cfvo type="formula" val="1"/>
@@ -1553,12 +1646,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H13">
+  <conditionalFormatting sqref="H14:H15">
     <cfRule type="containsText" dxfId="10" priority="19" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H13))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H13">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H14))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H14:H15">
     <cfRule type="colorScale" priority="20">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -1570,12 +1663,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H14:H15">
+  <conditionalFormatting sqref="H16">
     <cfRule type="containsText" dxfId="9" priority="17" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H14))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H14:H15">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H16))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H16">
     <cfRule type="colorScale" priority="18">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -1587,13 +1680,13 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H16">
-    <cfRule type="containsText" dxfId="8" priority="15" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H16))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H16">
-    <cfRule type="colorScale" priority="16">
+  <conditionalFormatting sqref="H19">
+    <cfRule type="containsText" dxfId="8" priority="9" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H19))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H19">
+    <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="formula" val="0"/>
         <cfvo type="formula" val="1"/>
@@ -1604,13 +1697,13 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H19">
-    <cfRule type="containsText" dxfId="7" priority="7" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H19))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H19">
-    <cfRule type="colorScale" priority="8">
+  <conditionalFormatting sqref="H17">
+    <cfRule type="containsText" dxfId="7" priority="13" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H17))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H17">
+    <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="formula" val="0"/>
         <cfvo type="formula" val="1"/>
@@ -1621,12 +1714,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H17">
+  <conditionalFormatting sqref="H18">
     <cfRule type="containsText" dxfId="6" priority="11" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H17))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H17">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H18))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H18">
     <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -1638,13 +1731,13 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H18">
-    <cfRule type="containsText" dxfId="5" priority="9" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H18))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H18">
-    <cfRule type="colorScale" priority="10">
+  <conditionalFormatting sqref="H20 H22">
+    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H20))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H20 H22">
+    <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="formula" val="0"/>
         <cfvo type="formula" val="1"/>
@@ -1655,12 +1748,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H20">
+  <conditionalFormatting sqref="H21">
     <cfRule type="containsText" dxfId="4" priority="3" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H20))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H20">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H21))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H21">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -1672,12 +1765,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H21">
-    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H21))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H21">
+  <conditionalFormatting sqref="H23">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H23))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H23">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>

--- a/Collections/EURO/Lithuania/#EURO#Lithuania#Commemorative#[2015-present]#UNC.xlsx
+++ b/Collections/EURO/Lithuania/#EURO#Lithuania#Commemorative#[2015-present]#UNC.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lord_Alexator\Documents\CoinCollection\Collections\EURO\Lithuania\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C14347AD-A544-4957-A12F-B38981F2EF56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{671720A7-6469-400E-BB9B-7154524843EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -549,14 +549,6 @@
   </cellStyles>
   <dxfs count="15">
     <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -564,6 +556,14 @@
     </dxf>
     <dxf>
       <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <fill>
@@ -674,9 +674,9 @@
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="№" dataDxfId="3"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Link" dataDxfId="2" dataCellStyle="Гиперссылка"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description (single table, table set, mintage, prices):" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="№" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Link" dataDxfId="1" dataCellStyle="Гиперссылка"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description (single table, table set, mintage, prices):" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="1" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -1511,7 +1511,7 @@
     </row>
     <row r="22" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="22">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>54</v>
@@ -1736,7 +1736,7 @@
       <formula>NOT(ISERROR(SEARCH(("*-"),(H20))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H20 H22">
+  <conditionalFormatting sqref="H22 H20">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -1766,7 +1766,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H23">
-    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H23))))</formula>
     </cfRule>
   </conditionalFormatting>
